--- a/sampleprojects/Poker/excel/Poker_map.xlsx
+++ b/sampleprojects/Poker/excel/Poker_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>MAP: Poker</t>
   </si>
@@ -116,6 +116,30 @@
   </si>
   <si>
     <t># Multiple instance entities</t>
+  </si>
+  <si>
+    <t>## CREATE ENTITIES (entity | tag | id | list)</t>
+  </si>
+  <si>
+    <t>players</t>
+  </si>
+  <si>
+    <t>decisions</t>
+  </si>
+  <si>
+    <t>## ENTITIES (name | number: 1 or *)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>## INITIALIZATION (entity | push)</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -836,6 +860,98 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
     </row>
+    <row r="28">
+      <c r="A28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/sampleprojects/Poker/excel/Poker_map.xlsx
+++ b/sampleprojects/Poker/excel/Poker_map.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>MAP: Poker</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>## CREATE ENTITIES (entity | tag | id | list)</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>players</t>
@@ -870,10 +873,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6</v>
@@ -884,39 +887,43 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
@@ -926,31 +933,41 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
